--- a/docs/20261016_ミーティング議題.xlsx
+++ b/docs/20261016_ミーティング議題.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koyama\Desktop\ricca_doc\20260925_OOP\20261016_実装２\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\terafes_03\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C965A4-5E1B-4227-A03F-C24059D82E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3864860D-7D7C-424D-AB8F-75794FC183D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="69">
   <si>
     <t>10/16 ミーティング議題</t>
   </si>
@@ -258,6 +258,109 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>マツイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>運用で当日朝消すことにする</t>
+    <rPh sb="0" eb="2">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>トウジツアサ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>仕様書には50秒以内など記載。</t>
+    <rPh sb="0" eb="3">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>基本機能が仕上がってからやり方含め対応</t>
+    <rPh sb="0" eb="4">
+      <t>キホンキノウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カタフク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>対応方法</t>
+    <rPh sb="0" eb="4">
+      <t>タイオウホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>▼ミーティングで決まったこと</t>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>状況</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ー</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>優先順位順に本日対応</t>
+    <rPh sb="0" eb="4">
+      <t>ユウセンジュンイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホンジツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>本日すぐ対応</t>
+    <rPh sb="0" eb="2">
+      <t>ホンジツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイオウ</t>
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
@@ -723,7 +826,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -732,14 +835,20 @@
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="24.44140625" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.2">
+    <row r="1" spans="1:8" ht="22.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18">
+    <row r="2" spans="1:8">
+      <c r="G2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
@@ -758,8 +867,14 @@
       <c r="F3" s="10" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="72">
+      <c r="G3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -778,8 +893,14 @@
       <c r="F4" s="11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="72">
+      <c r="G4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="72">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -798,8 +919,11 @@
       <c r="F5" s="11" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="36">
+      <c r="G5" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="36">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -818,8 +942,11 @@
       <c r="F6" s="11" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="54">
+      <c r="G6" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="54">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -838,8 +965,14 @@
       <c r="F7" s="12" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="54">
+      <c r="G7" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="54">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -858,8 +991,14 @@
       <c r="F8" s="12" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="54">
+      <c r="G8" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="54">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -878,8 +1017,11 @@
       <c r="F9" s="12" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="36">
+      <c r="G9" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="36">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -898,8 +1040,11 @@
       <c r="F10" s="12" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="54">
+      <c r="G10" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="54">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -918,8 +1063,11 @@
       <c r="F11" s="12" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="36">
+      <c r="G11" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="72">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -938,8 +1086,11 @@
       <c r="F12" s="12" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="54">
+      <c r="G12" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="54">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -955,8 +1106,14 @@
       <c r="E13" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="72">
+      <c r="G13" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="72">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -975,8 +1132,11 @@
       <c r="F14" s="12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="54">
+      <c r="G14" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="54">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -995,8 +1155,11 @@
       <c r="F15" s="12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="36">
+      <c r="G15" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="36">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1014,6 +1177,9 @@
       </c>
       <c r="F16" s="12" t="s">
         <v>53</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6">

--- a/docs/20261016_ミーティング議題.xlsx
+++ b/docs/20261016_ミーティング議題.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\terafes_03\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koyama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3864860D-7D7C-424D-AB8F-75794FC183D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10422BC0-1179-48B1-BF3F-E6C8D0819292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
   <si>
     <t>10/16 ミーティング議題</t>
   </si>
@@ -922,6 +922,9 @@
       <c r="G5" s="11" t="s">
         <v>61</v>
       </c>
+      <c r="H5" s="11" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="36">
       <c r="A6" s="2">
@@ -945,6 +948,9 @@
       <c r="G6" s="11" t="s">
         <v>68</v>
       </c>
+      <c r="H6" s="11" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="54">
       <c r="A7" s="2">
@@ -1043,6 +1049,9 @@
       <c r="G10" s="12" t="s">
         <v>67</v>
       </c>
+      <c r="H10" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="54">
       <c r="A11" s="2">
@@ -1066,6 +1075,9 @@
       <c r="G11" s="12" t="s">
         <v>67</v>
       </c>
+      <c r="H11" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="72">
       <c r="A12" s="2">
@@ -1135,6 +1147,9 @@
       <c r="G14" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="H14" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="54">
       <c r="A15" s="2">
@@ -1158,6 +1173,9 @@
       <c r="G15" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="H15" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="36">
       <c r="A16" s="2">
@@ -1180,6 +1198,9 @@
       </c>
       <c r="G16" s="12" t="s">
         <v>68</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6">

--- a/docs/20261016_ミーティング議題.xlsx
+++ b/docs/20261016_ミーティング議題.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koyama\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\terafes_03\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10422BC0-1179-48B1-BF3F-E6C8D0819292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC0F646-97DB-411C-B269-EEF2A7052DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">議題!$A$3:$E$16</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,11 +28,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="124">
   <si>
     <t>10/16 ミーティング議題</t>
   </si>
   <si>
+    <t>▼ミーティングで決まったこと</t>
+  </si>
+  <si>
     <t>元の番号</t>
   </si>
   <si>
@@ -48,6 +51,15 @@
     <t>理由</t>
   </si>
   <si>
+    <t>担当者</t>
+  </si>
+  <si>
+    <t>対応方法</t>
+  </si>
+  <si>
+    <t>状況</t>
+  </si>
+  <si>
     <t>進み具合の共有</t>
   </si>
   <si>
@@ -60,6 +72,15 @@
     <t>最初に共有して、各自がすぐ動けるように</t>
   </si>
   <si>
+    <t>全員</t>
+  </si>
+  <si>
+    <t>ー</t>
+  </si>
+  <si>
+    <t>完了</t>
+  </si>
+  <si>
     <t>スペースキーまたはカウントダウン</t>
   </si>
   <si>
@@ -72,6 +93,9 @@
     <t>小さい子が手を戻す前に始まってしまう</t>
   </si>
   <si>
+    <t>基本機能が仕上がってからやり方含め対応</t>
+  </si>
+  <si>
     <t>リセットにパスワード</t>
   </si>
   <si>
@@ -84,6 +108,12 @@
     <t>来場者が押すと、全部の記録が消える</t>
   </si>
   <si>
+    <t>松井</t>
+  </si>
+  <si>
+    <t>本日すぐ対応</t>
+  </si>
+  <si>
     <t>本日のトップが「--」のままになる</t>
   </si>
   <si>
@@ -93,6 +123,12 @@
     <t>展示当日に起きる。決めるのは運用だけなので1分で済む</t>
   </si>
   <si>
+    <t>（全員）</t>
+  </si>
+  <si>
+    <t>運用で当日朝消すことにする</t>
+  </si>
+  <si>
     <t>曲の長さ</t>
   </si>
   <si>
@@ -102,6 +138,12 @@
     <t>確認だけ（曲データを直すときに決まる）</t>
   </si>
   <si>
+    <t>（確認）</t>
+  </si>
+  <si>
+    <t>仕様書には50秒以内など記載。</t>
+  </si>
+  <si>
     <t>本日のトップに名前</t>
   </si>
   <si>
@@ -132,6 +174,10 @@
     <t>「100%」が何か分からない</t>
   </si>
   <si>
+    <t>岡野（result.css）
+松井（index.html）</t>
+  </si>
+  <si>
     <t>追加の曲</t>
   </si>
   <si>
@@ -141,6 +187,10 @@
     <t>11〜13 が終わってから</t>
   </si>
   <si>
+    <t>中山
+松井</t>
+  </si>
+  <si>
     <t>5回目までの分担</t>
   </si>
   <si>
@@ -159,12 +209,18 @@
     <t>不具合。仕様の変更なしで直せる。12より先に直す</t>
   </si>
   <si>
+    <t>中山</t>
+  </si>
+  <si>
     <t>伴奏のコード進行を曲ごとに</t>
   </si>
   <si>
     <t>伴奏は見本のまま、3曲とも C → Am → F → G のくり返しで、メロディと合わない所がある（ジングルベルは今でも違和感あり）。曲データに chords（1小節に1つ、省略可）を足し、audio.js でそれを使う。直すのは charts.js・audio.js（中山さん）だけ。</t>
   </si>
   <si>
+    <t>メロディと合わず、曲として未完成。仕様書8.1の変更が必要</t>
+  </si>
+  <si>
     <t>天国と地獄の譜面を本物に</t>
   </si>
   <si>
@@ -177,191 +233,195 @@
     <t>優先度　A：直さないと展示できない／B：遊びやすさに関わる／C：あるとうれしい</t>
   </si>
   <si>
-    <t>担当者</t>
-    <rPh sb="0" eb="2">
-      <t>タントウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シャ</t>
+    <t>▼追加の議題（10/16 夜に整理。月曜 10/19 のスタディアワー・各自の時間で対応）</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>本日のトップを広げる（本日のトップ3）</t>
+  </si>
+  <si>
+    <t>タイトル画面の本日のトップを、曲ごとの上位3人（名前つき）に広げる。4列×3行で、4曲・6文字の名前でも収まることを確認済み。タイトル画面の作り直し（丸い「あそぶ」、リセットを隅へ）と一緒に作る。仕様書3.2・8.3の変更。（直すファイル：screens.js・style.css）</t>
+  </si>
+  <si>
+    <t>名前を入れた人がうれしい。ランキング一覧（19）の代わりになる</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>追加の曲（ジングルベルと天国と地獄の間）</t>
+  </si>
+  <si>
+    <t>難易度の差を埋めるため、間に1曲追加。候補は「ジ・エンターテイナー」か「猫ふんじゃった」（どちらも著作権切れ）。曲は SONGS の末尾に足す（ランキングの保存キーが曲の番号のため）。カードが4枚になるので小さくする。（直すファイル：charts.js、style.css）</t>
+  </si>
+  <si>
+    <t>ジングルベルと天国と地獄の難易度の差が大きい</t>
+  </si>
+  <si>
+    <t>中山（charts.js）
+松井（style.css：カード4枚）</t>
+  </si>
+  <si>
+    <t>月曜</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>画面を、認定証のようなかわいいトーンに</t>
+  </si>
+  <si>
+    <t>画面の雰囲気を認定証にそろえる</t>
+  </si>
+  <si>
+    <t>松井（作る）
+岡野（仕上げ）</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>4体目のキャラ「こっそりスパイウェア」</t>
+  </si>
+  <si>
+    <t>4レーンとも別のキャラにする案。全員のファイルにまたがり、仕様書5.2・6章も変わる。</t>
+  </si>
+  <si>
+    <t>見送り</t>
+  </si>
+  <si>
+    <t>影響が大きい。テストが近い</t>
+  </si>
+  <si>
+    <t>見送り（岡野さんの提案で取りやめ）</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>ミスでレーンが揺れる</t>
+  </si>
+  <si>
+    <t>ミスしたとき、レーンを短く揺らす。揺れの CSS は中山さんの新しいファイル fx.css に書く（style.css の衝突を避けるため）。index.html の読み込みの1行は松井。（直すファイル：view.js・game.js・fx.css）</t>
+  </si>
+  <si>
+    <t>ミスしたことが目で分かる</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>ヒットでキラキラがはじける</t>
+  </si>
+  <si>
+    <t>今の粒を、星形などのキラキラに変える。</t>
+  </si>
+  <si>
+    <t>実装済み</t>
+  </si>
+  <si>
+    <t>さらに直すかは、やってもやらなくてもよい</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>豆知識の文を本物に</t>
+  </si>
+  <si>
+    <t>仮の3つを、10個くらいの本物の豆知識に書きかえる。1つ40文字くらい。IPAなどで確かめる。（直すファイル：tips.js）</t>
+  </si>
+  <si>
+    <t>仮のままでは展示の中身にならない</t>
+  </si>
+  <si>
+    <t>岡野</t>
+  </si>
+  <si>
+    <t>月曜の前に各自の時間で</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>ランキング一覧画面（O-05）</t>
+  </si>
+  <si>
+    <t>全曲のランキングを一覧で見る画面。本日のトップ3（6）で代わりにする。要件定義書の O-05 に「見送り」と書く。</t>
+  </si>
+  <si>
+    <t>本日のトップ3で十分</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>【仮】ボタンと見本の値の片づけ</t>
+  </si>
+  <si>
+    <t>モックアップの【仮】切り替えボタンと、index.html の見本の値（レーン・ウイルス・スコアなど）を消す。（直すファイル：index.html・style.css・screens.js）</t>
+  </si>
+  <si>
+    <t>展示で見えてしまう</t>
+  </si>
+  <si>
+    <t>岡野さんの仕上げの後（5回目でも可）</t>
+  </si>
+  <si>
+    <t>通しのテスト（1920×1080・1366×768）</t>
+  </si>
+  <si>
+    <t>全部入った後に、通しで遊んで確認する。結果は docs/test.md。</t>
+  </si>
+  <si>
+    <t>展示の前に必ず確かめる</t>
+  </si>
+  <si>
+    <t>5回目（10/22）の授業で</t>
+  </si>
+  <si>
+    <t>完了日</t>
+    <rPh sb="0" eb="3">
+      <t>カンリョウビ</t>
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>全員</t>
-    <rPh sb="0" eb="2">
-      <t>ゼンイン</t>
+    <t>⇒追加の議題へ</t>
+    <rPh sb="1" eb="3">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ギダイ</t>
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>松井</t>
-    <rPh sb="0" eb="2">
-      <t>マツイ</t>
-    </rPh>
+    <t>中山（game.js）
+松井（screens.js）</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>（確認）</t>
-    <rPh sb="1" eb="3">
-      <t>カクニン</t>
-    </rPh>
+    <t>基本機能が仕上がってからやり方含め対応
+⇒スペースキーにする</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>中山</t>
-    <rPh sb="0" eb="2">
-      <t>ナカヤマ</t>
-    </rPh>
+    <t>優先順位順に対応</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>メロディと合わず、曲として未完成。仕様書8.1の変更が必要</t>
-    <rPh sb="13" eb="16">
-      <t>ミカンセイ</t>
-    </rPh>
+    <t>月曜より前</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>（全員）</t>
-    <rPh sb="1" eb="3">
-      <t>ゼンイン</t>
-    </rPh>
+    <t>タイトル画面は月曜より前、セレクト・プレイ画面は月曜</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>岡野（result.css）
-松井（index.html）</t>
-    <rPh sb="0" eb="2">
-      <t>オカノ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>マツイ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>中山
-松井</t>
-    <rPh sb="0" eb="2">
-      <t>ナカヤマ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>マツイ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>中山（game.js）
-（松井（screens.js））</t>
-    <rPh sb="0" eb="2">
-      <t>ナカヤマ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>マツイ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>運用で当日朝消すことにする</t>
-    <rPh sb="0" eb="2">
-      <t>ウンヨウ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>トウジツアサ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ケ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>仕様書には50秒以内など記載。</t>
-    <rPh sb="0" eb="3">
-      <t>シヨウショ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>イナイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>キサイ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>基本機能が仕上がってからやり方含め対応</t>
-    <rPh sb="0" eb="4">
-      <t>キホンキノウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>カタフク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>タイオウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>対応方法</t>
-    <rPh sb="0" eb="4">
-      <t>タイオウホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>▼ミーティングで決まったこと</t>
-    <rPh sb="8" eb="9">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>状況</t>
-    <rPh sb="0" eb="2">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>完了</t>
-    <rPh sb="0" eb="2">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>ー</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>優先順位順に本日対応</t>
-    <rPh sb="0" eb="4">
-      <t>ユウセンジュンイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ジュン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ホンジツ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>タイオウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>本日すぐ対応</t>
-    <rPh sb="0" eb="2">
-      <t>ホンジツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タイオウ</t>
-    </rPh>
+    <t>岡野さんの認定証（result.css）に合わせて、画面の見た目をそろえる。ボタンの水色の枠は、白い縁を太く＋ピンクの光に変える。松井が作り、岡野さんが見て直したい所を伝える。style.css への反映は松井。（直すファイル：style.css）</t>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -369,7 +429,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,8 +479,37 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF999999"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF999999"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,6 +535,11 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -487,7 +581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -515,10 +609,29 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -826,7 +939,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -835,383 +948,670 @@
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="24.44140625" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="18.77734375" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22.2">
+    <row r="1" spans="1:8" ht="22.2" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="G2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="72">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72" customHeight="1">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="72">
+        <v>15</v>
+      </c>
+      <c r="H4" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="90">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="36">
+        <v>119</v>
+      </c>
+      <c r="H5" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="36" customHeight="1">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="54">
+        <v>27</v>
+      </c>
+      <c r="H6" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="54" customHeight="1">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="54">
+        <v>32</v>
+      </c>
+      <c r="H7" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="54" customHeight="1">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="54">
+        <v>37</v>
+      </c>
+      <c r="H8" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="54" customHeight="1">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="G9" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="36">
+        <v>120</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="36" customHeight="1">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="54">
+        <v>120</v>
+      </c>
+      <c r="H10" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="54" customHeight="1">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="72">
+        <v>120</v>
+      </c>
+      <c r="H11" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="72" customHeight="1">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="54">
+        <v>21</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="54" customHeight="1">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="72">
+        <v>15</v>
+      </c>
+      <c r="H13" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="72" customHeight="1">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="54">
+        <v>27</v>
+      </c>
+      <c r="H14" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="54" customHeight="1">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="36">
+        <v>27</v>
+      </c>
+      <c r="H15" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="36" customHeight="1">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="18">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.6" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="19.8">
+      <c r="A20" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="18">
+      <c r="A21" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="72">
+      <c r="A22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" s="11"/>
+    </row>
+    <row r="23" spans="1:8" ht="72">
+      <c r="A23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" s="11"/>
+    </row>
+    <row r="24" spans="1:8" ht="72.599999999999994" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="H24" s="11"/>
+    </row>
+    <row r="25" spans="1:8" ht="72">
+      <c r="A25" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="54">
+      <c r="A26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="11"/>
+    </row>
+    <row r="27" spans="1:8" ht="72">
+      <c r="A27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="15.6">
-      <c r="A18" s="8" t="s">
-        <v>48</v>
-      </c>
+    </row>
+    <row r="28" spans="1:8" ht="54">
+      <c r="A28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="1:8" ht="36">
+      <c r="A29" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="72">
+      <c r="A30" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="H30" s="11"/>
+    </row>
+    <row r="31" spans="1:8" ht="54">
+      <c r="A31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:E16" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup fitToHeight="0" orientation="landscape"/>
+  <ignoredErrors>
+    <ignoredError sqref="A22:A23 A24:A27 A28:A30" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/20261016_ミーティング議題.xlsx
+++ b/docs/20261016_ミーティング議題.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\terafes_03\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koyama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC0F646-97DB-411C-B269-EEF2A7052DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB9199E-E43A-43A9-B76E-31ECAB9261E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="124">
   <si>
     <t>10/16 ミーティング議題</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>対応方法</t>
-  </si>
-  <si>
-    <t>状況</t>
   </si>
   <si>
     <t>進み具合の共有</t>
@@ -422,6 +419,13 @@
   </si>
   <si>
     <t>岡野さんの認定証（result.css）に合わせて、画面の見た目をそろえる。ボタンの水色の枠は、白い縁を太く＋ピンクの光に変える。松井が作り、岡野さんが見て直したい所を伝える。style.css への反映は松井。（直すファイル：style.css）</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>松井：10/17</t>
+    <rPh sb="0" eb="2">
+      <t>マツイ</t>
+    </rPh>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -985,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72" customHeight="1">
@@ -993,22 +997,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>15</v>
       </c>
       <c r="H4" s="18">
         <v>46311</v>
@@ -1019,22 +1023,22 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F5" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>119</v>
       </c>
       <c r="H5" s="18">
         <v>46311</v>
@@ -1045,22 +1049,22 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="G6" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>27</v>
       </c>
       <c r="H6" s="18">
         <v>46311</v>
@@ -1071,22 +1075,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="G7" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>32</v>
       </c>
       <c r="H7" s="18">
         <v>46311</v>
@@ -1097,22 +1101,22 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>36</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>37</v>
       </c>
       <c r="H8" s="18">
         <v>46311</v>
@@ -1123,25 +1127,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="F9" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="36" customHeight="1">
@@ -1149,22 +1153,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="F10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H10" s="18">
         <v>46311</v>
@@ -1175,22 +1179,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>48</v>
-      </c>
       <c r="G11" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H11" s="18">
         <v>46311</v>
@@ -1201,25 +1205,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>52</v>
-      </c>
       <c r="G12" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="54" customHeight="1">
@@ -1227,19 +1231,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="G13" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H13" s="18">
         <v>46311</v>
@@ -1250,22 +1254,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>59</v>
-      </c>
       <c r="G14" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H14" s="18">
         <v>46311</v>
@@ -1276,22 +1280,22 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="F15" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H15" s="18">
         <v>46311</v>
@@ -1302,22 +1306,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="F16" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H16" s="18">
         <v>46311</v>
@@ -1325,12 +1329,12 @@
     </row>
     <row r="18" spans="1:8" ht="15.6" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="19.8">
       <c r="A20" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="18">
@@ -1356,252 +1360,256 @@
         <v>8</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="72">
       <c r="A22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="F22" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="H22" s="11"/>
+        <v>120</v>
+      </c>
+      <c r="H22" s="18">
+        <v>46312</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="72">
       <c r="A23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="G23" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>77</v>
       </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" spans="1:8" ht="72.599999999999994" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" s="11" t="s">
+    </row>
+    <row r="25" spans="1:8" ht="36">
+      <c r="A25" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="H24" s="11"/>
-    </row>
-    <row r="25" spans="1:8" ht="72">
-      <c r="A25" s="14" t="s">
+      <c r="B25" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="C25" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="E25" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>87</v>
-      </c>
       <c r="H25" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="54">
       <c r="A26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="11"/>
+    </row>
+    <row r="27" spans="1:8" ht="54">
+      <c r="A27" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="11"/>
-    </row>
-    <row r="27" spans="1:8" ht="72">
-      <c r="A27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F27" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G27" s="11" t="s">
+      <c r="H27" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="36">
+      <c r="A28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H27" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="54">
-      <c r="A28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="G28" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="H28" s="11"/>
     </row>
     <row r="29" spans="1:8" ht="36">
       <c r="A29" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="C29" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="D29" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" s="15" t="s">
+      <c r="F29" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="36">
+      <c r="A30" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="72">
-      <c r="A30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="11" t="s">
+      <c r="H30" s="11"/>
+    </row>
+    <row r="31" spans="1:8" ht="36">
+      <c r="A31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H30" s="11"/>
-    </row>
-    <row r="31" spans="1:8" ht="54">
-      <c r="A31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>115</v>
       </c>
       <c r="H31" s="11"/>
     </row>
@@ -1609,7 +1617,7 @@
   <autoFilter ref="A3:E16" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" orientation="landscape"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A22:A23 A24:A27 A28:A30" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/docs/20261016_ミーティング議題.xlsx
+++ b/docs/20261016_ミーティング議題.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koyama\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\terafes_03\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB9199E-E43A-43A9-B76E-31ECAB9261E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC5E120-3E94-4F23-95DC-0D6DCE90ACF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="125">
   <si>
     <t>10/16 ミーティング議題</t>
   </si>
@@ -424,6 +424,14 @@
   <si>
     <t>松井：10/17</t>
     <rPh sb="0" eb="2">
+      <t>マツイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>中山
+松井</t>
+    <rPh sb="3" eb="5">
       <t>マツイ</t>
     </rPh>
     <phoneticPr fontId="6"/>
@@ -1411,7 +1419,9 @@
       <c r="G23" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="H23" s="11"/>
+      <c r="H23" s="11" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="72.599999999999994" customHeight="1">
       <c r="A24" s="2" t="s">
@@ -1482,7 +1492,7 @@
         <v>90</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>76</v>

--- a/docs/20261016_ミーティング議題.xlsx
+++ b/docs/20261016_ミーティング議題.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\terafes_03\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koyama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC5E120-3E94-4F23-95DC-0D6DCE90ACF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCABF0B-F313-4FD6-B0FB-803CDA0CCD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="121">
   <si>
     <t>10/16 ミーティング議題</t>
   </si>
@@ -257,13 +257,6 @@
     <t>ジングルベルと天国と地獄の難易度の差が大きい</t>
   </si>
   <si>
-    <t>中山（charts.js）
-松井（style.css：カード4枚）</t>
-  </si>
-  <si>
-    <t>月曜</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -273,10 +266,6 @@
     <t>画面の雰囲気を認定証にそろえる</t>
   </si>
   <si>
-    <t>松井（作る）
-岡野（仕上げ）</t>
-  </si>
-  <si>
     <t>15</t>
   </si>
   <si>
@@ -301,9 +290,6 @@
     <t>ミスでレーンが揺れる</t>
   </si>
   <si>
-    <t>ミスしたとき、レーンを短く揺らす。揺れの CSS は中山さんの新しいファイル fx.css に書く（style.css の衝突を避けるため）。index.html の読み込みの1行は松井。（直すファイル：view.js・game.js・fx.css）</t>
-  </si>
-  <si>
     <t>ミスしたことが目で分かる</t>
   </si>
   <si>
@@ -355,28 +341,10 @@
     <t>20</t>
   </si>
   <si>
-    <t>【仮】ボタンと見本の値の片づけ</t>
-  </si>
-  <si>
     <t>モックアップの【仮】切り替えボタンと、index.html の見本の値（レーン・ウイルス・スコアなど）を消す。（直すファイル：index.html・style.css・screens.js）</t>
   </si>
   <si>
     <t>展示で見えてしまう</t>
-  </si>
-  <si>
-    <t>岡野さんの仕上げの後（5回目でも可）</t>
-  </si>
-  <si>
-    <t>通しのテスト（1920×1080・1366×768）</t>
-  </si>
-  <si>
-    <t>全部入った後に、通しで遊んで確認する。結果は docs/test.md。</t>
-  </si>
-  <si>
-    <t>展示の前に必ず確かめる</t>
-  </si>
-  <si>
-    <t>5回目（10/22）の授業で</t>
   </si>
   <si>
     <t>完了日</t>
@@ -418,22 +386,57 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>岡野さんの認定証（result.css）に合わせて、画面の見た目をそろえる。ボタンの水色の枠は、白い縁を太く＋ピンクの光に変える。松井が作り、岡野さんが見て直したい所を伝える。style.css への反映は松井。（直すファイル：style.css）</t>
+    <t>松井</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>松井：10/17</t>
-    <rPh sb="0" eb="2">
-      <t>マツイ</t>
+    <t>ミスしたとき、レーンを短く揺らす。揺れの CSS は中山さんの新しいファイル fx.css に書く（style.css の衝突を避けるため）。index.html の読み込みの1行は松井。（直すファイル：view.js・game.js・fx.css）</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t xml:space="preserve">中山
+</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>直すファイル：view.js・game.js（fx.css は作らず、JavaScript でプレイ画面をずらす形になった）
+index.html の読み込みは不要</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>１曲だけではなく、３曲足して、全部で６曲にする</t>
+    <rPh sb="1" eb="2">
+      <t>キョク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キョク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゼンブ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>キョク</t>
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>中山
-松井</t>
-    <rPh sb="3" eb="5">
-      <t>マツイ</t>
-    </rPh>
+    <t>中山（charts.js）
+松井（style.css：カード６枚）</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>【仮】ボタンと見本の値の片づけ</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>仕上げの後（5回目でも可）</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>岡野さんの認定証（result.css）に合わせて、画面の見た目をそろえる。ボタンの水色の枠は、白い縁を太く＋ピンクの光に変える。style.css への反映は松井。（直すファイル：style.css）</t>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -951,7 +954,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -959,8 +962,8 @@
     <col min="3" max="3" width="80" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="24.44140625" customWidth="1"/>
-    <col min="7" max="7" width="18.77734375" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="7" max="7" width="29.44140625" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -997,7 +1000,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72" customHeight="1">
@@ -1043,10 +1046,10 @@
         <v>19</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H5" s="18">
         <v>46311</v>
@@ -1150,10 +1153,10 @@
         <v>25</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="36" customHeight="1">
@@ -1176,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="H10" s="18">
         <v>46311</v>
@@ -1202,7 +1205,7 @@
         <v>47</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="H11" s="18">
         <v>46311</v>
@@ -1231,7 +1234,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="54" customHeight="1">
@@ -1368,7 +1371,7 @@
         <v>8</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="72">
@@ -1391,7 +1394,7 @@
         <v>25</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H22" s="18">
         <v>46312</v>
@@ -1414,112 +1417,114 @@
         <v>74</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>123</v>
+        <v>116</v>
+      </c>
+      <c r="H23" s="18">
+        <v>46314</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="72.599999999999994" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>123</v>
+        <v>111</v>
+      </c>
+      <c r="H24" s="18">
+        <v>46314</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="36">
       <c r="A25" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H25" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="90">
+      <c r="A26" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="54">
-      <c r="A26" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="B26" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="11"/>
+        <v>115</v>
+      </c>
+      <c r="H26" s="18">
+        <v>46314</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="54">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>58</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>15</v>
@@ -1527,101 +1532,81 @@
     </row>
     <row r="28" spans="1:8" ht="36">
       <c r="A28" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="H28" s="11"/>
+        <v>97</v>
+      </c>
+      <c r="H28" s="18">
+        <v>46314</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="36">
       <c r="A29" s="14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="36">
       <c r="A30" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="H30" s="11"/>
-    </row>
-    <row r="31" spans="1:8" ht="36">
-      <c r="A31" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="H31" s="11"/>
+        <v>119</v>
+      </c>
+      <c r="H30" s="18">
+        <v>46314</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:E16" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
